--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B2" t="n">
         <v>106355</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R2" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B3" t="n">
         <v>106355</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R3" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B4" t="n">
-        <v>96073</v>
+        <v>106355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B5" t="n">
-        <v>106355</v>
+        <v>96073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R5" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129589847</v>
+        <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626798</v>
+        <v>626809</v>
       </c>
       <c r="R14" t="n">
-        <v>6711379</v>
+        <v>6711322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129589842</v>
+        <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>92203</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626809</v>
+        <v>626798</v>
       </c>
       <c r="R15" t="n">
-        <v>6711322</v>
+        <v>6711379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104198</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B2" t="n">
         <v>106355</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R2" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B3" t="n">
         <v>106355</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R3" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>106355</v>
+        <v>96073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R4" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>96073</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>106355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R6" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B10" t="n">
-        <v>75161</v>
+        <v>104198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R10" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B11" t="n">
-        <v>104198</v>
+        <v>75161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R11" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B4" t="n">
-        <v>96073</v>
+        <v>91517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589839</v>
+        <v>129589853</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>96073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626912</v>
       </c>
       <c r="R5" t="n">
-        <v>6711252</v>
+        <v>6711433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B10" t="n">
-        <v>104198</v>
+        <v>75161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R10" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>75161</v>
+        <v>104198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R11" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589839</v>
+        <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>91517</v>
+        <v>96102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626771</v>
+        <v>626912</v>
       </c>
       <c r="R4" t="n">
-        <v>6711252</v>
+        <v>6711433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>96073</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129589849</v>
       </c>
       <c r="B10" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98644</v>
+        <v>98673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>104227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,38 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B17" t="n">
-        <v>104198</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2205,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B10" t="n">
-        <v>75182</v>
+        <v>104239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R10" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B11" t="n">
-        <v>104227</v>
+        <v>75187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R11" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104227</v>
+        <v>104239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98673</v>
+        <v>98685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>104227</v>
+        <v>104239</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B4" t="n">
-        <v>96114</v>
+        <v>91552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B5" t="n">
-        <v>91551</v>
+        <v>106397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R5" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B6" t="n">
-        <v>106396</v>
+        <v>96115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R6" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B10" t="n">
-        <v>104239</v>
+        <v>75188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R10" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>75187</v>
+        <v>104240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R11" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104239</v>
+        <v>104240</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104239</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B10" t="n">
-        <v>75188</v>
+        <v>104240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R10" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B11" t="n">
-        <v>104240</v>
+        <v>75188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R11" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129589839</v>
       </c>
       <c r="B4" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B5" t="n">
-        <v>106397</v>
+        <v>96120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R5" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>96115</v>
+        <v>106402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R6" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B10" t="n">
-        <v>104240</v>
+        <v>75193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R10" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>75188</v>
+        <v>104245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R11" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104240</v>
+        <v>104245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>104240</v>
+        <v>104245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>106402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R4" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589840</v>
+        <v>129589839</v>
       </c>
       <c r="B6" t="n">
-        <v>106402</v>
+        <v>91557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626804</v>
+        <v>626771</v>
       </c>
       <c r="R6" t="n">
-        <v>6711238</v>
+        <v>6711252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>106402</v>
+        <v>96120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R4" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B5" t="n">
-        <v>96120</v>
+        <v>106402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R5" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>104245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,38 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B17" t="n">
-        <v>104245</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2205,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B4" t="n">
-        <v>96120</v>
+        <v>106402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B5" t="n">
-        <v>106402</v>
+        <v>96120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R5" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B2" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R2" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B3" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R3" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>106402</v>
+        <v>96124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R4" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>96120</v>
+        <v>91561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>91557</v>
+        <v>106406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R6" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>104245</v>
+        <v>104249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104245</v>
+        <v>104249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129589842</v>
+        <v>129589847</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626809</v>
+        <v>626798</v>
       </c>
       <c r="R14" t="n">
-        <v>6711322</v>
+        <v>6711379</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129589847</v>
+        <v>129589842</v>
       </c>
       <c r="B15" t="n">
-        <v>98752</v>
+        <v>92247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626798</v>
+        <v>626809</v>
       </c>
       <c r="R15" t="n">
-        <v>6711379</v>
+        <v>6711322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>104245</v>
+        <v>104249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R2" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R3" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B5" t="n">
-        <v>91561</v>
+        <v>106408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R5" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589840</v>
+        <v>129589839</v>
       </c>
       <c r="B6" t="n">
-        <v>106406</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626804</v>
+        <v>626771</v>
       </c>
       <c r="R6" t="n">
-        <v>6711238</v>
+        <v>6711252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>104249</v>
+        <v>104251</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104249</v>
+        <v>104251</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129589847</v>
+        <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>92249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626798</v>
+        <v>626809</v>
       </c>
       <c r="R14" t="n">
-        <v>6711379</v>
+        <v>6711322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129589842</v>
+        <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>92247</v>
+        <v>98758</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626809</v>
+        <v>626798</v>
       </c>
       <c r="R15" t="n">
-        <v>6711322</v>
+        <v>6711379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104249</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589840</v>
+        <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>106408</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626804</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6711238</v>
+        <v>6711252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>106408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R6" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>104251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,38 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B17" t="n">
-        <v>104251</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2205,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104251</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B2" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R2" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B3" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R3" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B4" t="n">
-        <v>96126</v>
+        <v>106418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B6" t="n">
-        <v>106408</v>
+        <v>96136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R6" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>104251</v>
+        <v>104261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104251</v>
+        <v>104261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>104261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,38 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B17" t="n">
-        <v>104251</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2205,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104261</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589835</v>
+        <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626845</v>
+        <v>626847</v>
       </c>
       <c r="R2" t="n">
-        <v>6711325</v>
+        <v>6711442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589850</v>
+        <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626847</v>
+        <v>626845</v>
       </c>
       <c r="R3" t="n">
-        <v>6711442</v>
+        <v>6711325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589840</v>
+        <v>129589853</v>
       </c>
       <c r="B4" t="n">
-        <v>106418</v>
+        <v>96140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626804</v>
+        <v>626912</v>
       </c>
       <c r="R4" t="n">
-        <v>6711238</v>
+        <v>6711433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589839</v>
+        <v>129589840</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>106422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626804</v>
       </c>
       <c r="R5" t="n">
-        <v>6711252</v>
+        <v>6711238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589853</v>
+        <v>129589839</v>
       </c>
       <c r="B6" t="n">
-        <v>96136</v>
+        <v>91566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626912</v>
+        <v>626771</v>
       </c>
       <c r="R6" t="n">
-        <v>6711433</v>
+        <v>6711252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B10" t="n">
-        <v>75193</v>
+        <v>104265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R10" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B11" t="n">
-        <v>104261</v>
+        <v>75196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R11" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104261</v>
+        <v>104265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>104261</v>
+        <v>104265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B4" t="n">
-        <v>96140</v>
+        <v>106422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R4" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589840</v>
+        <v>129589839</v>
       </c>
       <c r="B5" t="n">
-        <v>106422</v>
+        <v>91566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626804</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6711238</v>
+        <v>6711252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589839</v>
+        <v>129589853</v>
       </c>
       <c r="B6" t="n">
-        <v>91566</v>
+        <v>96140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626771</v>
+        <v>626912</v>
       </c>
       <c r="R6" t="n">
-        <v>6711252</v>
+        <v>6711433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>104265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,38 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B17" t="n">
-        <v>104265</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2205,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589850</v>
       </c>
       <c r="B2" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129589835</v>
       </c>
       <c r="B3" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589840</v>
+        <v>129589839</v>
       </c>
       <c r="B4" t="n">
-        <v>106422</v>
+        <v>91569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626804</v>
+        <v>626771</v>
       </c>
       <c r="R4" t="n">
-        <v>6711238</v>
+        <v>6711252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589839</v>
+        <v>129589853</v>
       </c>
       <c r="B5" t="n">
-        <v>91566</v>
+        <v>96143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626912</v>
       </c>
       <c r="R5" t="n">
-        <v>6711252</v>
+        <v>6711433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589853</v>
+        <v>129589840</v>
       </c>
       <c r="B6" t="n">
-        <v>96140</v>
+        <v>106425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626912</v>
+        <v>626804</v>
       </c>
       <c r="R6" t="n">
-        <v>6711433</v>
+        <v>6711238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129589857</v>
       </c>
       <c r="B7" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129589848</v>
       </c>
       <c r="B8" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129589845</v>
       </c>
       <c r="B9" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589843</v>
+        <v>129589849</v>
       </c>
       <c r="B10" t="n">
-        <v>104265</v>
+        <v>75199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626864</v>
+        <v>626851</v>
       </c>
       <c r="R10" t="n">
-        <v>6711312</v>
+        <v>6711447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589849</v>
+        <v>129589843</v>
       </c>
       <c r="B11" t="n">
-        <v>75196</v>
+        <v>104268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626851</v>
+        <v>626864</v>
       </c>
       <c r="R11" t="n">
-        <v>6711447</v>
+        <v>6711312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129589846</v>
       </c>
       <c r="B12" t="n">
-        <v>104265</v>
+        <v>104268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129589841</v>
       </c>
       <c r="B13" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129589842</v>
       </c>
       <c r="B14" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129589847</v>
       </c>
       <c r="B15" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589836</v>
+        <v>129589856</v>
       </c>
       <c r="B16" t="n">
-        <v>104265</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2044,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626837</v>
+        <v>626859</v>
       </c>
       <c r="R16" t="n">
-        <v>6711342</v>
+        <v>6711382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,6 +2108,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589856</v>
+        <v>129589836</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>104268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,38 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626859</v>
+        <v>626837</v>
       </c>
       <c r="R17" t="n">
-        <v>6711382</v>
+        <v>6711342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2239,7 +2239,7 @@
         <v>129589838</v>
       </c>
       <c r="B18" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589850</v>
+        <v>129589842</v>
       </c>
       <c r="B2" t="n">
-        <v>106425</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626847</v>
+        <v>626809</v>
       </c>
       <c r="R2" t="n">
-        <v>6711442</v>
+        <v>6711322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589835</v>
+        <v>129589853</v>
       </c>
       <c r="B3" t="n">
-        <v>106425</v>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626845</v>
+        <v>626912</v>
       </c>
       <c r="R3" t="n">
-        <v>6711325</v>
+        <v>6711433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129589839</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589853</v>
+        <v>129589849</v>
       </c>
       <c r="B5" t="n">
-        <v>96143</v>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626912</v>
+        <v>626851</v>
       </c>
       <c r="R5" t="n">
-        <v>6711433</v>
+        <v>6711447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,45 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589840</v>
+        <v>129589856</v>
       </c>
       <c r="B6" t="n">
-        <v>106425</v>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626804</v>
+        <v>626859</v>
       </c>
       <c r="R6" t="n">
-        <v>6711238</v>
+        <v>6711382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,6 +1138,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129589857</v>
+        <v>129589841</v>
       </c>
       <c r="B7" t="n">
-        <v>106425</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626871</v>
+        <v>626781</v>
       </c>
       <c r="R7" t="n">
-        <v>6711391</v>
+        <v>6711298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129589848</v>
+        <v>129589847</v>
       </c>
       <c r="B8" t="n">
-        <v>106425</v>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626781</v>
+        <v>626798</v>
       </c>
       <c r="R8" t="n">
-        <v>6711400</v>
+        <v>6711379</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129589845</v>
+        <v>129589855</v>
       </c>
       <c r="B9" t="n">
-        <v>106425</v>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626806</v>
+        <v>626921</v>
       </c>
       <c r="R9" t="n">
-        <v>6711382</v>
+        <v>6711434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589849</v>
+        <v>129589854</v>
       </c>
       <c r="B10" t="n">
-        <v>75199</v>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626851</v>
+        <v>626921</v>
       </c>
       <c r="R10" t="n">
-        <v>6711447</v>
+        <v>6711434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,27 +1557,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589843</v>
+        <v>129589835</v>
       </c>
       <c r="B11" t="n">
-        <v>104268</v>
+        <v>106812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626864</v>
+        <v>626845</v>
       </c>
       <c r="R11" t="n">
-        <v>6711312</v>
+        <v>6711325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,27 +1654,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129589846</v>
+        <v>129589838</v>
       </c>
       <c r="B12" t="n">
-        <v>104268</v>
+        <v>106812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1680,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626806</v>
+        <v>626821</v>
       </c>
       <c r="R12" t="n">
-        <v>6711382</v>
+        <v>6711354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129589841</v>
+        <v>129589840</v>
       </c>
       <c r="B13" t="n">
-        <v>98714</v>
+        <v>106812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626781</v>
+        <v>626804</v>
       </c>
       <c r="R13" t="n">
-        <v>6711298</v>
+        <v>6711238</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129589842</v>
+        <v>129589845</v>
       </c>
       <c r="B14" t="n">
-        <v>92255</v>
+        <v>106812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626809</v>
+        <v>626806</v>
       </c>
       <c r="R14" t="n">
-        <v>6711322</v>
+        <v>6711382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129589847</v>
+        <v>129589848</v>
       </c>
       <c r="B15" t="n">
-        <v>98775</v>
+        <v>106812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626798</v>
+        <v>626781</v>
       </c>
       <c r="R15" t="n">
-        <v>6711379</v>
+        <v>6711400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,49 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589856</v>
+        <v>129589850</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>106812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>V om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626859</v>
+        <v>626847</v>
       </c>
       <c r="R16" t="n">
-        <v>6711382</v>
+        <v>6711442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2108,11 +2113,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,27 +2139,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589836</v>
+        <v>129589857</v>
       </c>
       <c r="B17" t="n">
-        <v>104268</v>
+        <v>106812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626837</v>
+        <v>626871</v>
       </c>
       <c r="R17" t="n">
-        <v>6711342</v>
+        <v>6711391</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,27 +2236,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129589838</v>
+        <v>129589836</v>
       </c>
       <c r="B18" t="n">
-        <v>106425</v>
+        <v>104627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626821</v>
+        <v>626837</v>
       </c>
       <c r="R18" t="n">
-        <v>6711354</v>
+        <v>6711342</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2330,6 +2330,200 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129589843</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>V om Storfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626864</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6711312</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129589846</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>V om Storfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626806</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6711382</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19703-2025 artfynd.xlsx
+++ b/artfynd/A 19703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589853</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589839</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589855</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589854</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589835</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589840</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589845</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589848</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589850</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589857</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589836</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589843</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,8 +2619,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>